--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9025,0.0110,0.0157,0.0518</t>
-  </si>
-  <si>
-    <t>0.0207,0.0071,0.0060,0.9877</t>
-  </si>
-  <si>
-    <t>0.6643,0.0606,0.0050,0.2061</t>
-  </si>
-  <si>
-    <t>0.2273,0.0025,0.0183,0.8430</t>
-  </si>
-  <si>
-    <t>0.9952,0.0041,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0031,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9877,0.0117,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9932,0.0039,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9821,0.0120,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9886,0.0131,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0053,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9933,0.0022,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.8356,0.0994,0.0616,0.0079</t>
-  </si>
-  <si>
-    <t>0.3602,0.0173,0.8029,0.0029</t>
-  </si>
-  <si>
-    <t>0.1403,0.0347,0.8678,0.0011</t>
-  </si>
-  <si>
-    <t>0.0495,0.0109,0.9337,0.0365</t>
-  </si>
-  <si>
-    <t>0.7723,0.0282,0.2147,0.0305</t>
-  </si>
-  <si>
-    <t>0.0104,0.9797,0.0012,0.0024</t>
-  </si>
-  <si>
-    <t>0.0493,0.9513,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.5936,0.5426,0.0082,0.0020</t>
-  </si>
-  <si>
-    <t>0.1980,0.8551,0.0031,0.0021</t>
-  </si>
-  <si>
-    <t>0.0212,0.9721,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.4946,0.0092,0.3290,0.1579</t>
-  </si>
-  <si>
-    <t>0.5066,0.0154,0.6356,0.0102</t>
-  </si>
-  <si>
-    <t>0.0128,0.0077,0.9753,0.0046</t>
-  </si>
-  <si>
-    <t>0.2353,0.0066,0.8522,0.0167</t>
-  </si>
-  <si>
-    <t>0.1717,0.0043,0.9209,0.0046</t>
-  </si>
-  <si>
-    <t>0.2176,0.0058,0.8630,0.0096</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9948,0.0087</t>
-  </si>
-  <si>
-    <t>0.5415,0.6038,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.3177,0.3551,0.4241,0.0117</t>
-  </si>
-  <si>
-    <t>0.0004,0.0046,0.9948,0.0039</t>
-  </si>
-  <si>
-    <t>0.0075,0.9210,0.3389,0.0002</t>
-  </si>
-  <si>
-    <t>0.6266,0.2739,0.0133,0.0670</t>
-  </si>
-  <si>
-    <t>0.3110,0.3554,0.4364,0.0101</t>
-  </si>
-  <si>
-    <t>0.3030,0.7528,0.0119,0.0036</t>
-  </si>
-  <si>
-    <t>0.1620,0.7978,0.1501,0.0079</t>
-  </si>
-  <si>
-    <t>0.0465,0.7901,0.1316,0.0452</t>
-  </si>
-  <si>
-    <t>0.0245,0.0796,0.9096,0.0459</t>
-  </si>
-  <si>
-    <t>0.0321,0.1568,0.8020,0.0863</t>
-  </si>
-  <si>
-    <t>0.0606,0.0161,0.9384,0.0082</t>
-  </si>
-  <si>
-    <t>0.0306,0.7015,0.5704,0.0163</t>
-  </si>
-  <si>
-    <t>0.0177,0.7124,0.5288,0.0132</t>
-  </si>
-  <si>
-    <t>0.0040,0.0832,0.9495,0.0276</t>
-  </si>
-  <si>
-    <t>0.3259,0.1005,0.0508,0.6797</t>
-  </si>
-  <si>
-    <t>0.0088,0.9576,0.0165,0.0471</t>
-  </si>
-  <si>
-    <t>0.0066,0.9555,0.2634,0.0021</t>
-  </si>
-  <si>
-    <t>0.0047,0.9383,0.0096,0.1409</t>
-  </si>
-  <si>
-    <t>0.0019,0.0274,0.9869,0.0071</t>
-  </si>
-  <si>
-    <t>0.0037,0.0408,0.9899,0.0003</t>
-  </si>
-  <si>
-    <t>0.1098,0.0200,0.9129,0.0032</t>
-  </si>
-  <si>
-    <t>0.1150,0.0076,0.9331,0.0021</t>
-  </si>
-  <si>
-    <t>0.0030,0.0213,0.9881,0.0039</t>
-  </si>
-  <si>
-    <t>0.0079,0.0241,0.9791,0.0004</t>
-  </si>
-  <si>
-    <t>0.9515,0.0633,0.0020,0.0011</t>
-  </si>
-  <si>
-    <t>0.9013,0.0931,0.0205,0.0030</t>
-  </si>
-  <si>
-    <t>0.9861,0.0131,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.0322,0.0372,0.9697,0.0044</t>
-  </si>
-  <si>
-    <t>0.9716,0.0165,0.0007,0.0030</t>
-  </si>
-  <si>
-    <t>0.9780,0.0183,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9744,0.0250,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.0018,0.9023,0.8342,0.0008</t>
-  </si>
-  <si>
-    <t>0.0108,0.1631,0.9721,0.0040</t>
-  </si>
-  <si>
-    <t>0.0156,0.0261,0.9639,0.0119</t>
-  </si>
-  <si>
-    <t>0.0006,0.9406,0.8897,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0017,0.9951,0.0034</t>
-  </si>
-  <si>
-    <t>0.0480,0.9197,0.0413,0.0105</t>
-  </si>
-  <si>
-    <t>0.0586,0.9420,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.5489,0.0308,0.5736,0.0185</t>
-  </si>
-  <si>
-    <t>0.2821,0.0922,0.7239,0.0053</t>
-  </si>
-  <si>
-    <t>0.0074,0.0324,0.9861,0.0021</t>
-  </si>
-  <si>
-    <t>0.0098,0.8526,0.5257,0.0039</t>
-  </si>
-  <si>
-    <t>0.0068,0.7826,0.7625,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9810,0.1716,0.0020</t>
-  </si>
-  <si>
-    <t>0.0028,0.8376,0.9080,0.0006</t>
-  </si>
-  <si>
-    <t>0.0257,0.0032,0.0122,0.9804</t>
-  </si>
-  <si>
-    <t>0.0004,0.0192,0.0011,0.9991</t>
-  </si>
-  <si>
-    <t>0.0232,0.0010,0.0009,0.9930</t>
-  </si>
-  <si>
-    <t>0.0231,0.0035,0.0058,0.9858</t>
-  </si>
-  <si>
-    <t>0.0759,0.0113,0.0057,0.9670</t>
-  </si>
-  <si>
-    <t>0.0267,0.0031,0.0028,0.9890</t>
-  </si>
-  <si>
-    <t>0.0035,0.7769,0.8887,0.0009</t>
-  </si>
-  <si>
-    <t>0.0035,0.7059,0.9489,0.0009</t>
-  </si>
-  <si>
-    <t>0.0021,0.9173,0.7392,0.0014</t>
-  </si>
-  <si>
-    <t>0.0125,0.4949,0.8585,0.0021</t>
-  </si>
-  <si>
-    <t>0.0027,0.8707,0.8448,0.0002</t>
-  </si>
-  <si>
-    <t>0.0097,0.6765,0.7825,0.0023</t>
-  </si>
-  <si>
-    <t>0.9842,0.0159,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9844,0.0179,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9837,0.0190,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9929,0.0039,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9848,0.0158,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9865,0.0109,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9850,0.0088,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.9691,0.0339,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9890,0.0020,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9952,0.0029,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0025,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0055,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9940,0.0063,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0040,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9886,0.0044,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.1121,0.0179,0.9419,0.0026</t>
-  </si>
-  <si>
-    <t>0.0067,0.0040,0.9865,0.0016</t>
-  </si>
-  <si>
-    <t>0.8094,0.0066,0.1578,0.0273</t>
-  </si>
-  <si>
-    <t>0.0156,0.0089,0.9852,0.0004</t>
-  </si>
-  <si>
-    <t>0.4093,0.6780,0.0136,0.0042</t>
-  </si>
-  <si>
-    <t>0.0237,0.9641,0.0025,0.0020</t>
-  </si>
-  <si>
-    <t>0.0691,0.8951,0.0004,0.0089</t>
-  </si>
-  <si>
-    <t>0.4399,0.6759,0.0037,0.0028</t>
-  </si>
-  <si>
-    <t>0.0381,0.9413,0.0023,0.0040</t>
-  </si>
-  <si>
-    <t>0.0388,0.9532,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.3504,0.7013,0.0278,0.0053</t>
-  </si>
-  <si>
-    <t>0.6653,0.1993,0.1610,0.0312</t>
-  </si>
-  <si>
-    <t>0.3022,0.0121,0.8227,0.0072</t>
-  </si>
-  <si>
-    <t>0.4672,0.3099,0.2525,0.0370</t>
-  </si>
-  <si>
-    <t>0.5061,0.2698,0.2601,0.0991</t>
-  </si>
-  <si>
-    <t>0.3598,0.1361,0.3221,0.4503</t>
-  </si>
-  <si>
-    <t>0.0042,0.9778,0.0187,0.0116</t>
-  </si>
-  <si>
-    <t>0.0099,0.9399,0.0243,0.0873</t>
-  </si>
-  <si>
-    <t>0.0125,0.9403,0.0236,0.0324</t>
-  </si>
-  <si>
-    <t>0.0015,0.9738,0.3760,0.0018</t>
-  </si>
-  <si>
-    <t>0.1440,0.8750,0.0367,0.0006</t>
-  </si>
-  <si>
-    <t>0.4928,0.5847,0.0207,0.0009</t>
-  </si>
-  <si>
-    <t>0.5623,0.5152,0.0133,0.0032</t>
-  </si>
-  <si>
-    <t>0.9722,0.0211,0.0026,0.0024</t>
-  </si>
-  <si>
-    <t>0.9730,0.0078,0.0022,0.0053</t>
-  </si>
-  <si>
-    <t>0.9790,0.0057,0.0006,0.0046</t>
-  </si>
-  <si>
-    <t>0.9636,0.0166,0.0020,0.0057</t>
-  </si>
-  <si>
-    <t>0.9895,0.0029,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9334,0.0543,0.0195,0.0011</t>
-  </si>
-  <si>
-    <t>0.9835,0.0074,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9825,0.0034,0.0007,0.0041</t>
-  </si>
-  <si>
-    <t>0.0050,0.4370,0.9573,0.0020</t>
-  </si>
-  <si>
-    <t>0.0026,0.5502,0.9431,0.0003</t>
-  </si>
-  <si>
-    <t>0.0049,0.0727,0.9835,0.0003</t>
-  </si>
-  <si>
-    <t>0.0895,0.2393,0.7582,0.0157</t>
-  </si>
-  <si>
-    <t>0.8647,0.0162,0.1107,0.0131</t>
-  </si>
-  <si>
-    <t>0.7245,0.1444,0.1230,0.0537</t>
-  </si>
-  <si>
-    <t>0.7465,0.0040,0.3612,0.0156</t>
-  </si>
-  <si>
-    <t>0.3924,0.4619,0.2194,0.0174</t>
-  </si>
-  <si>
-    <t>0.2141,0.0121,0.0021,0.9108</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0034,0.9987</t>
-  </si>
-  <si>
-    <t>0.0011,0.0705,0.0013,0.9976</t>
-  </si>
-  <si>
-    <t>0.0167,0.0034,0.0026,0.9916</t>
-  </si>
-  <si>
-    <t>0.0159,0.8651,0.5619,0.0035</t>
-  </si>
-  <si>
-    <t>0.9819,0.0126,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.3300,0.6764,0.0061,0.0225</t>
-  </si>
-  <si>
-    <t>0.9809,0.0067,0.0013,0.0031</t>
-  </si>
-  <si>
-    <t>0.9448,0.0561,0.0024,0.0026</t>
-  </si>
-  <si>
-    <t>0.9810,0.0050,0.0048,0.0023</t>
-  </si>
-  <si>
-    <t>0.2953,0.0106,0.0154,0.8352</t>
-  </si>
-  <si>
-    <t>0.9737,0.0144,0.0036,0.0023</t>
-  </si>
-  <si>
-    <t>0.0012,0.4975,0.9378,0.0062</t>
-  </si>
-  <si>
-    <t>0.9067,0.0004,0.0167,0.0382</t>
-  </si>
-  <si>
-    <t>0.9776,0.0025,0.0034,0.0067</t>
-  </si>
-  <si>
-    <t>0.1046,0.8741,0.0066,0.0131</t>
-  </si>
-  <si>
-    <t>0.5612,0.5220,0.0145,0.0061</t>
-  </si>
-  <si>
-    <t>0.8891,0.0683,0.0437,0.0049</t>
-  </si>
-  <si>
-    <t>0.5449,0.4922,0.0314,0.0223</t>
-  </si>
-  <si>
-    <t>0.8456,0.0515,0.1579,0.0060</t>
-  </si>
-  <si>
-    <t>0.7638,0.2697,0.0186,0.0082</t>
-  </si>
-  <si>
-    <t>0.9794,0.0110,0.0047,0.0019</t>
-  </si>
-  <si>
-    <t>0.9668,0.0129,0.0044,0.0050</t>
-  </si>
-  <si>
-    <t>0.9902,0.0021,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9878,0.0020,0.0031,0.0024</t>
-  </si>
-  <si>
-    <t>0.9874,0.0031,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9729,0.0038,0.0008,0.0093</t>
-  </si>
-  <si>
-    <t>0.9805,0.0037,0.0005,0.0051</t>
-  </si>
-  <si>
-    <t>0.9884,0.0059,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.3065,0.7626,0.0024,0.0033</t>
-  </si>
-  <si>
-    <t>0.6878,0.4609,0.0060,0.0010</t>
-  </si>
-  <si>
-    <t>0.4612,0.6435,0.0079,0.0018</t>
-  </si>
-  <si>
-    <t>0.8840,0.0429,0.0965,0.0115</t>
-  </si>
-  <si>
-    <t>0.9771,0.0211,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.8233,0.2337,0.0030,0.0031</t>
-  </si>
-  <si>
-    <t>0.9227,0.0693,0.0178,0.0031</t>
-  </si>
-  <si>
-    <t>0.9294,0.0570,0.0029,0.0054</t>
-  </si>
-  <si>
-    <t>0.0085,0.0714,0.9838,0.0010</t>
-  </si>
-  <si>
-    <t>0.9637,0.0297,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.0047,0.0038,0.9921,0.0009</t>
-  </si>
-  <si>
-    <t>0.0314,0.3128,0.9045,0.0198</t>
-  </si>
-  <si>
-    <t>0.0099,0.0029,0.9885,0.0020</t>
-  </si>
-  <si>
-    <t>0.0170,0.1473,0.9557,0.0048</t>
-  </si>
-  <si>
-    <t>0.0238,0.0148,0.9679,0.0029</t>
-  </si>
-  <si>
-    <t>0.0660,0.0058,0.9571,0.0012</t>
-  </si>
-  <si>
-    <t>0.0060,0.0296,0.9817,0.0007</t>
-  </si>
-  <si>
-    <t>0.3883,0.0615,0.6578,0.0505</t>
-  </si>
-  <si>
-    <t>0.2901,0.0606,0.7233,0.0136</t>
-  </si>
-  <si>
-    <t>0.6643,0.0454,0.3948,0.0152</t>
-  </si>
-  <si>
-    <t>0.3753,0.1315,0.5182,0.0038</t>
-  </si>
-  <si>
-    <t>0.2263,0.0212,0.8566,0.0035</t>
-  </si>
-  <si>
-    <t>0.6866,0.0853,0.3065,0.0118</t>
-  </si>
-  <si>
-    <t>0.6191,0.1551,0.2700,0.0453</t>
-  </si>
-  <si>
-    <t>0.3568,0.0223,0.7700,0.0065</t>
-  </si>
-  <si>
-    <t>0.6890,0.4100,0.0091,0.0010</t>
-  </si>
-  <si>
-    <t>0.8131,0.3414,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9256,0.0902,0.0113,0.0014</t>
-  </si>
-  <si>
-    <t>0.9616,0.0594,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.5178,0.6308,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.6312,0.1125,0.3168,0.0145</t>
-  </si>
-  <si>
-    <t>0.8321,0.0205,0.2112,0.0050</t>
-  </si>
-  <si>
-    <t>0.7930,0.0183,0.0459,0.1291</t>
-  </si>
-  <si>
-    <t>0.8280,0.0043,0.2452,0.0061</t>
-  </si>
-  <si>
-    <t>0.7364,0.0170,0.3323,0.0155</t>
-  </si>
-  <si>
-    <t>0.0741,0.0177,0.8954,0.0571</t>
-  </si>
-  <si>
-    <t>0.1827,0.2534,0.5883,0.0235</t>
-  </si>
-  <si>
-    <t>0.0071,0.5161,0.8870,0.0034</t>
-  </si>
-  <si>
-    <t>0.0056,0.1096,0.9790,0.0006</t>
-  </si>
-  <si>
-    <t>0.0351,0.3586,0.7547,0.0048</t>
-  </si>
-  <si>
-    <t>0.9769,0.0029,0.0004,0.0082</t>
-  </si>
-  <si>
-    <t>0.9884,0.0079,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9684,0.0136,0.0016,0.0041</t>
-  </si>
-  <si>
-    <t>0.9918,0.0048,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9787,0.0222,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9857,0.0045,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.9830,0.0159,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9882,0.0093,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0967,0.0134,0.9302,0.0126</t>
-  </si>
-  <si>
-    <t>0.4820,0.3727,0.1922,0.0210</t>
-  </si>
-  <si>
-    <t>0.8187,0.0583,0.1592,0.0119</t>
-  </si>
-  <si>
-    <t>0.0131,0.1200,0.9172,0.0059</t>
-  </si>
-  <si>
-    <t>0.0020,0.0478,0.9823,0.0017</t>
-  </si>
-  <si>
-    <t>0.0369,0.6827,0.4461,0.0100</t>
-  </si>
-  <si>
-    <t>0.0003,0.0059,0.9972,0.0014</t>
-  </si>
-  <si>
-    <t>0.0474,0.0082,0.9456,0.0106</t>
-  </si>
-  <si>
-    <t>0.0129,0.0090,0.9709,0.0116</t>
-  </si>
-  <si>
-    <t>0.0438,0.0229,0.9278,0.0121</t>
-  </si>
-  <si>
-    <t>0.1148,0.0498,0.8756,0.0033</t>
-  </si>
-  <si>
-    <t>0.7107,0.0137,0.3440,0.0307</t>
-  </si>
-  <si>
-    <t>0.8337,0.0082,0.1388,0.0345</t>
-  </si>
-  <si>
-    <t>0.4994,0.0076,0.7057,0.0050</t>
-  </si>
-  <si>
-    <t>0.9678,0.0148,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9898,0.0078,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0015,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9870,0.0106,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9896,0.0019,0.0003,0.0023</t>
-  </si>
-  <si>
-    <t>0.9865,0.0102,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9956,0.0018,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9876,0.0024,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.0795,0.0622,0.8415,0.0038</t>
-  </si>
-  <si>
-    <t>0.0035,0.0764,0.9840,0.0008</t>
-  </si>
-  <si>
-    <t>0.0214,0.0868,0.8983,0.0256</t>
-  </si>
-  <si>
-    <t>0.1439,0.0785,0.7497,0.0192</t>
-  </si>
-  <si>
-    <t>0.0055,0.0075,0.9801,0.0088</t>
-  </si>
-  <si>
-    <t>0.0476,0.0337,0.6294,0.5712</t>
-  </si>
-  <si>
-    <t>0.3082,0.0440,0.6646,0.0812</t>
-  </si>
-  <si>
-    <t>0.0186,0.0431,0.8436,0.1940</t>
-  </si>
-  <si>
-    <t>0.7162,0.0029,0.0033,0.4353</t>
-  </si>
-  <si>
-    <t>0.0759,0.0057,0.0067,0.9652</t>
-  </si>
-  <si>
-    <t>0.0139,0.0341,0.0052,0.9891</t>
-  </si>
-  <si>
-    <t>0.0041,0.0001,0.0021,0.9963</t>
-  </si>
-  <si>
-    <t>0.0016,0.0017,0.0004,0.9991</t>
-  </si>
-  <si>
-    <t>0.8610,0.0063,0.0209,0.1079</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.4650,0.1441,0.0276,0.4085</t>
+  </si>
+  <si>
+    <t>0.0190,0.0027,0.0022,0.9926</t>
+  </si>
+  <si>
+    <t>0.8338,0.0238,0.0075,0.0978</t>
+  </si>
+  <si>
+    <t>0.0288,0.0066,0.0016,0.9895</t>
+  </si>
+  <si>
+    <t>0.9953,0.0018,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0022,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9887,0.0113,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9826,0.0211,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9791,0.0229,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9896,0.0145,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0020,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.7015,0.1276,0.2530,0.0220</t>
+  </si>
+  <si>
+    <t>0.1497,0.0863,0.7991,0.0094</t>
+  </si>
+  <si>
+    <t>0.0874,0.0335,0.9062,0.0006</t>
+  </si>
+  <si>
+    <t>0.0795,0.0084,0.9246,0.0278</t>
+  </si>
+  <si>
+    <t>0.7575,0.0839,0.1548,0.0151</t>
+  </si>
+  <si>
+    <t>0.0568,0.9423,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.0880,0.9290,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.2786,0.7686,0.0196,0.0016</t>
+  </si>
+  <si>
+    <t>0.0776,0.9321,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.0421,0.9577,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.7968,0.0067,0.3030,0.0071</t>
+  </si>
+  <si>
+    <t>0.5282,0.0389,0.2979,0.1059</t>
+  </si>
+  <si>
+    <t>0.0416,0.0019,0.9483,0.0343</t>
+  </si>
+  <si>
+    <t>0.1346,0.0082,0.8853,0.0307</t>
+  </si>
+  <si>
+    <t>0.1245,0.0028,0.9342,0.0054</t>
+  </si>
+  <si>
+    <t>0.0700,0.0116,0.9124,0.0473</t>
+  </si>
+  <si>
+    <t>0.0060,0.0034,0.9864,0.0042</t>
+  </si>
+  <si>
+    <t>0.6072,0.5426,0.0065,0.0021</t>
+  </si>
+  <si>
+    <t>0.6436,0.1571,0.2697,0.0086</t>
+  </si>
+  <si>
+    <t>0.0015,0.0144,0.9909,0.0023</t>
+  </si>
+  <si>
+    <t>0.0675,0.8365,0.1440,0.0014</t>
+  </si>
+  <si>
+    <t>0.6262,0.4718,0.0157,0.0074</t>
+  </si>
+  <si>
+    <t>0.4803,0.2169,0.2412,0.0015</t>
+  </si>
+  <si>
+    <t>0.7433,0.2728,0.0347,0.0023</t>
+  </si>
+  <si>
+    <t>0.0489,0.9019,0.1627,0.0037</t>
+  </si>
+  <si>
+    <t>0.0464,0.8078,0.0660,0.0728</t>
+  </si>
+  <si>
+    <t>0.0862,0.0068,0.7919,0.0365</t>
+  </si>
+  <si>
+    <t>0.0250,0.1168,0.8882,0.0332</t>
+  </si>
+  <si>
+    <t>0.0938,0.1313,0.8074,0.0286</t>
+  </si>
+  <si>
+    <t>0.0209,0.2617,0.8888,0.0117</t>
+  </si>
+  <si>
+    <t>0.0470,0.8221,0.2116,0.0057</t>
+  </si>
+  <si>
+    <t>0.0610,0.1272,0.8544,0.0274</t>
+  </si>
+  <si>
+    <t>0.2611,0.4029,0.0209,0.4766</t>
+  </si>
+  <si>
+    <t>0.0044,0.9518,0.0107,0.1687</t>
+  </si>
+  <si>
+    <t>0.0080,0.9445,0.0783,0.0095</t>
+  </si>
+  <si>
+    <t>0.0003,0.9902,0.0021,0.0295</t>
+  </si>
+  <si>
+    <t>0.0012,0.0061,0.9919,0.0052</t>
+  </si>
+  <si>
+    <t>0.0075,0.1975,0.9642,0.0006</t>
+  </si>
+  <si>
+    <t>0.0434,0.0043,0.9549,0.0124</t>
+  </si>
+  <si>
+    <t>0.0291,0.0023,0.9794,0.0042</t>
+  </si>
+  <si>
+    <t>0.0052,0.0058,0.9869,0.0049</t>
+  </si>
+  <si>
+    <t>0.0088,0.0215,0.9762,0.0024</t>
+  </si>
+  <si>
+    <t>0.9634,0.0319,0.0033,0.0022</t>
+  </si>
+  <si>
+    <t>0.8963,0.0882,0.0359,0.0035</t>
+  </si>
+  <si>
+    <t>0.9675,0.0224,0.0073,0.0021</t>
+  </si>
+  <si>
+    <t>0.0282,0.0731,0.9571,0.0101</t>
+  </si>
+  <si>
+    <t>0.9651,0.0342,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9911,0.0055,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9704,0.0353,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.0037,0.7776,0.9045,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.0169,0.9726,0.0241</t>
+  </si>
+  <si>
+    <t>0.0285,0.1118,0.9269,0.0101</t>
+  </si>
+  <si>
+    <t>0.0001,0.9465,0.9683,0.0000</t>
+  </si>
+  <si>
+    <t>0.0074,0.0253,0.9885,0.0005</t>
+  </si>
+  <si>
+    <t>0.2254,0.6772,0.2230,0.0197</t>
+  </si>
+  <si>
+    <t>0.0118,0.9757,0.0042,0.0025</t>
+  </si>
+  <si>
+    <t>0.9178,0.0152,0.1166,0.0025</t>
+  </si>
+  <si>
+    <t>0.3548,0.1382,0.6108,0.0070</t>
+  </si>
+  <si>
+    <t>0.0096,0.0629,0.9792,0.0019</t>
+  </si>
+  <si>
+    <t>0.0013,0.9352,0.6457,0.0009</t>
+  </si>
+  <si>
+    <t>0.0092,0.8184,0.7047,0.0057</t>
+  </si>
+  <si>
+    <t>0.0013,0.9743,0.0514,0.0273</t>
+  </si>
+  <si>
+    <t>0.0022,0.8330,0.9463,0.0007</t>
+  </si>
+  <si>
+    <t>0.0292,0.0027,0.0075,0.9813</t>
+  </si>
+  <si>
+    <t>0.0046,0.0037,0.0012,0.9971</t>
+  </si>
+  <si>
+    <t>0.0328,0.0097,0.0008,0.9886</t>
+  </si>
+  <si>
+    <t>0.0199,0.0020,0.0044,0.9895</t>
+  </si>
+  <si>
+    <t>0.0187,0.0040,0.0132,0.9825</t>
+  </si>
+  <si>
+    <t>0.0182,0.0114,0.0063,0.9873</t>
+  </si>
+  <si>
+    <t>0.0022,0.9068,0.8611,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.6475,0.9646,0.0004</t>
+  </si>
+  <si>
+    <t>0.0366,0.7452,0.3079,0.0314</t>
+  </si>
+  <si>
+    <t>0.0132,0.3473,0.9339,0.0028</t>
+  </si>
+  <si>
+    <t>0.0011,0.8970,0.7850,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.8939,0.4404,0.0004</t>
+  </si>
+  <si>
+    <t>0.9556,0.0693,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.9869,0.0119,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0124,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9869,0.0070,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9899,0.0064,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9927,0.0026,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9807,0.0123,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.9892,0.0050,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0100,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9977,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9934,0.0019,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0038,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0029,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0138,0.0055,0.9770,0.0144</t>
+  </si>
+  <si>
+    <t>0.0909,0.0080,0.9379,0.0043</t>
+  </si>
+  <si>
+    <t>0.7872,0.0084,0.0242,0.1420</t>
+  </si>
+  <si>
+    <t>0.1175,0.0052,0.9302,0.0065</t>
+  </si>
+  <si>
+    <t>0.0237,0.9588,0.0018,0.0043</t>
+  </si>
+  <si>
+    <t>0.0307,0.9578,0.0055,0.0014</t>
+  </si>
+  <si>
+    <t>0.0205,0.9574,0.0008,0.0057</t>
+  </si>
+  <si>
+    <t>0.1986,0.8544,0.0038,0.0014</t>
+  </si>
+  <si>
+    <t>0.1083,0.8983,0.0037,0.0024</t>
+  </si>
+  <si>
+    <t>0.0290,0.9654,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.1315,0.8688,0.0022,0.0029</t>
+  </si>
+  <si>
+    <t>0.8138,0.1084,0.0721,0.0162</t>
+  </si>
+  <si>
+    <t>0.4570,0.0511,0.5915,0.0050</t>
+  </si>
+  <si>
+    <t>0.1389,0.6315,0.2554,0.0163</t>
+  </si>
+  <si>
+    <t>0.6598,0.0748,0.3790,0.0176</t>
+  </si>
+  <si>
+    <t>0.3363,0.0895,0.0677,0.6120</t>
+  </si>
+  <si>
+    <t>0.0033,0.9750,0.0217,0.0203</t>
+  </si>
+  <si>
+    <t>0.0065,0.9765,0.0014,0.0093</t>
+  </si>
+  <si>
+    <t>0.0890,0.7947,0.0327,0.1492</t>
+  </si>
+  <si>
+    <t>0.0010,0.8914,0.9484,0.0003</t>
+  </si>
+  <si>
+    <t>0.0298,0.9561,0.0435,0.0004</t>
+  </si>
+  <si>
+    <t>0.6704,0.3151,0.0512,0.0027</t>
+  </si>
+  <si>
+    <t>0.3546,0.7229,0.0135,0.0013</t>
+  </si>
+  <si>
+    <t>0.9849,0.0118,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9760,0.0086,0.0039,0.0031</t>
+  </si>
+  <si>
+    <t>0.9815,0.0028,0.0005,0.0072</t>
+  </si>
+  <si>
+    <t>0.9887,0.0029,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9890,0.0039,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9782,0.0093,0.0087,0.0024</t>
+  </si>
+  <si>
+    <t>0.9803,0.0025,0.0011,0.0065</t>
+  </si>
+  <si>
+    <t>0.9846,0.0027,0.0007,0.0040</t>
+  </si>
+  <si>
+    <t>0.0183,0.5668,0.8573,0.0082</t>
+  </si>
+  <si>
+    <t>0.0117,0.6665,0.8227,0.0036</t>
+  </si>
+  <si>
+    <t>0.0084,0.0548,0.9677,0.0027</t>
+  </si>
+  <si>
+    <t>0.0347,0.3248,0.6606,0.0033</t>
+  </si>
+  <si>
+    <t>0.8113,0.0322,0.1753,0.0262</t>
+  </si>
+  <si>
+    <t>0.8608,0.0352,0.0769,0.0196</t>
+  </si>
+  <si>
+    <t>0.4984,0.0059,0.6970,0.0123</t>
+  </si>
+  <si>
+    <t>0.3666,0.2156,0.4907,0.0216</t>
+  </si>
+  <si>
+    <t>0.0529,0.0031,0.0049,0.9739</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0435,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.0172,0.0027,0.0022,0.9925</t>
+  </si>
+  <si>
+    <t>0.0070,0.7102,0.8805,0.0026</t>
+  </si>
+  <si>
+    <t>0.9774,0.0118,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.6979,0.3617,0.0092,0.0074</t>
+  </si>
+  <si>
+    <t>0.9746,0.0156,0.0033,0.0021</t>
+  </si>
+  <si>
+    <t>0.3536,0.7025,0.0167,0.0047</t>
+  </si>
+  <si>
+    <t>0.9868,0.0027,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.2613,0.0159,0.0196,0.8377</t>
+  </si>
+  <si>
+    <t>0.9761,0.0083,0.0065,0.0026</t>
+  </si>
+  <si>
+    <t>0.0019,0.0503,0.9783,0.0104</t>
+  </si>
+  <si>
+    <t>0.7491,0.0026,0.0169,0.2318</t>
+  </si>
+  <si>
+    <t>0.9087,0.0028,0.0258,0.0332</t>
+  </si>
+  <si>
+    <t>0.2462,0.7694,0.0136,0.0236</t>
+  </si>
+  <si>
+    <t>0.8105,0.1888,0.0122,0.0070</t>
+  </si>
+  <si>
+    <t>0.8762,0.0656,0.0662,0.0041</t>
+  </si>
+  <si>
+    <t>0.5216,0.4738,0.0312,0.0254</t>
+  </si>
+  <si>
+    <t>0.7539,0.2378,0.0411,0.0052</t>
+  </si>
+  <si>
+    <t>0.7496,0.2834,0.0156,0.0065</t>
+  </si>
+  <si>
+    <t>0.9912,0.0014,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9824,0.0062,0.0016,0.0023</t>
+  </si>
+  <si>
+    <t>0.9855,0.0083,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9887,0.0031,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9803,0.0058,0.0019,0.0035</t>
+  </si>
+  <si>
+    <t>0.9561,0.0242,0.0161,0.0020</t>
+  </si>
+  <si>
+    <t>0.9893,0.0040,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9882,0.0033,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.2489,0.8120,0.0065,0.0041</t>
+  </si>
+  <si>
+    <t>0.6071,0.5425,0.0050,0.0011</t>
+  </si>
+  <si>
+    <t>0.2798,0.8015,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.0885,0.2575,0.7653,0.0010</t>
+  </si>
+  <si>
+    <t>0.9846,0.0101,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9249,0.0604,0.0020,0.0047</t>
+  </si>
+  <si>
+    <t>0.9706,0.0262,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9826,0.0093,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.1629,0.9835,0.0009</t>
+  </si>
+  <si>
+    <t>0.9074,0.0933,0.0017,0.0045</t>
+  </si>
+  <si>
+    <t>0.0008,0.0023,0.9938,0.0061</t>
+  </si>
+  <si>
+    <t>0.0064,0.0558,0.9628,0.0198</t>
+  </si>
+  <si>
+    <t>0.1208,0.0212,0.8992,0.0052</t>
+  </si>
+  <si>
+    <t>0.0028,0.1090,0.9743,0.0033</t>
+  </si>
+  <si>
+    <t>0.0182,0.0199,0.9677,0.0123</t>
+  </si>
+  <si>
+    <t>0.0243,0.0056,0.9808,0.0007</t>
+  </si>
+  <si>
+    <t>0.0037,0.0030,0.9934,0.0015</t>
+  </si>
+  <si>
+    <t>0.2244,0.0363,0.8179,0.0152</t>
+  </si>
+  <si>
+    <t>0.2703,0.1039,0.6770,0.0186</t>
+  </si>
+  <si>
+    <t>0.2215,0.0111,0.8898,0.0045</t>
+  </si>
+  <si>
+    <t>0.2272,0.3925,0.3787,0.0032</t>
+  </si>
+  <si>
+    <t>0.3202,0.0136,0.8244,0.0021</t>
+  </si>
+  <si>
+    <t>0.6731,0.1153,0.2770,0.0308</t>
+  </si>
+  <si>
+    <t>0.7595,0.0526,0.2415,0.0194</t>
+  </si>
+  <si>
+    <t>0.4806,0.0809,0.5502,0.0261</t>
+  </si>
+  <si>
+    <t>0.7407,0.3562,0.0089,0.0005</t>
+  </si>
+  <si>
+    <t>0.8452,0.2547,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.6253,0.4734,0.0100,0.0009</t>
+  </si>
+  <si>
+    <t>0.9886,0.0113,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9808,0.0203,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.8110,0.0800,0.1275,0.0084</t>
+  </si>
+  <si>
+    <t>0.7170,0.0374,0.3410,0.0088</t>
+  </si>
+  <si>
+    <t>0.3045,0.1203,0.0345,0.6735</t>
+  </si>
+  <si>
+    <t>0.3985,0.1117,0.5882,0.0340</t>
+  </si>
+  <si>
+    <t>0.4173,0.0229,0.7138,0.0150</t>
+  </si>
+  <si>
+    <t>0.1589,0.0340,0.8428,0.0174</t>
+  </si>
+  <si>
+    <t>0.0217,0.0530,0.8203,0.1322</t>
+  </si>
+  <si>
+    <t>0.0192,0.1382,0.9143,0.0049</t>
+  </si>
+  <si>
+    <t>0.0871,0.1729,0.7333,0.0815</t>
+  </si>
+  <si>
+    <t>0.0732,0.4612,0.5259,0.0172</t>
+  </si>
+  <si>
+    <t>0.9646,0.0084,0.0001,0.0051</t>
+  </si>
+  <si>
+    <t>0.9860,0.0124,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9764,0.0062,0.0005,0.0038</t>
+  </si>
+  <si>
+    <t>0.9934,0.0043,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9760,0.0232,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9916,0.0032,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9762,0.0090,0.0005,0.0031</t>
+  </si>
+  <si>
+    <t>0.9564,0.0516,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.0728,0.0330,0.9370,0.0027</t>
+  </si>
+  <si>
+    <t>0.1489,0.4649,0.4478,0.0030</t>
+  </si>
+  <si>
+    <t>0.6952,0.2111,0.1170,0.0495</t>
+  </si>
+  <si>
+    <t>0.0021,0.0091,0.9912,0.0022</t>
+  </si>
+  <si>
+    <t>0.0030,0.0100,0.9902,0.0014</t>
+  </si>
+  <si>
+    <t>0.0110,0.0307,0.9635,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.0052,0.9925,0.0017</t>
+  </si>
+  <si>
+    <t>0.0950,0.0705,0.8155,0.0025</t>
+  </si>
+  <si>
+    <t>0.0024,0.0017,0.9880,0.0107</t>
+  </si>
+  <si>
+    <t>0.0197,0.0428,0.9158,0.0219</t>
+  </si>
+  <si>
+    <t>0.1637,0.0555,0.8131,0.0109</t>
+  </si>
+  <si>
+    <t>0.8348,0.0062,0.2100,0.0104</t>
+  </si>
+  <si>
+    <t>0.7479,0.0077,0.3836,0.0077</t>
+  </si>
+  <si>
+    <t>0.7561,0.0340,0.2516,0.0224</t>
+  </si>
+  <si>
+    <t>0.9781,0.0170,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9896,0.0112,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0067,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9864,0.0084,0.0019,0.0010</t>
+  </si>
+  <si>
+    <t>0.9832,0.0120,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9935,0.0053,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9936,0.0032,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9879,0.0046,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.0147,0.0629,0.9433,0.0017</t>
+  </si>
+  <si>
+    <t>0.0038,0.0266,0.9897,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.0565,0.9853,0.0017</t>
+  </si>
+  <si>
+    <t>0.2020,0.2819,0.3875,0.0057</t>
+  </si>
+  <si>
+    <t>0.0051,0.0101,0.9896,0.0015</t>
+  </si>
+  <si>
+    <t>0.0371,0.0102,0.9553,0.0212</t>
+  </si>
+  <si>
+    <t>0.0476,0.0042,0.9617,0.0039</t>
+  </si>
+  <si>
+    <t>0.0082,0.0839,0.9411,0.0111</t>
+  </si>
+  <si>
+    <t>0.6305,0.0012,0.0046,0.5359</t>
+  </si>
+  <si>
+    <t>0.0797,0.0467,0.0055,0.9583</t>
+  </si>
+  <si>
+    <t>0.0360,0.0200,0.0070,0.9779</t>
+  </si>
+  <si>
+    <t>0.0098,0.0004,0.0026,0.9944</t>
+  </si>
+  <si>
+    <t>0.0077,0.0004,0.0009,0.9967</t>
+  </si>
+  <si>
+    <t>0.8396,0.0318,0.0890,0.0382</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2536,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,10 +2550,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,10 +5098,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
